--- a/MILP/Input Data/master_problem_inputs_with_taste_draws.xlsx
+++ b/MILP/Input Data/master_problem_inputs_with_taste_draws.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atfan\Desktop\M.Sc DDS\Sem 4\Master's Thesis\Code\MILP\Input Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Atfan\Desktop\M.Sc DDS\Sem 4\Master's Thesis\Code\MILP\Results\Sensitivity analysis\Frequency\Fifty_Percent\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574DCCBE-8A7A-4139-9C1F-BC118E0F40BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09809E5D-9DC0-43B0-B310-293C5E8483A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OD_pairs" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Taste_Draws" sheetId="6" r:id="rId6"/>
     <sheet name="Global_Params" sheetId="7" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="56">
   <si>
     <t>origin_id</t>
   </si>
@@ -48,9 +51,6 @@
   </si>
   <si>
     <t>Aarau</t>
-  </si>
-  <si>
-    <t>Chiasso</t>
   </si>
   <si>
     <t>Stabio</t>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>exposure_TEU_per_day</t>
-  </si>
-  <si>
-    <t>Baselwolf</t>
   </si>
   <si>
     <t>t_hours</t>
@@ -194,10 +191,25 @@
     <t>taste_draw_count_R</t>
   </si>
   <si>
-    <t>0.10972690781987848</t>
+    <t>Bern</t>
   </si>
   <si>
-    <t>0.016649426669571643</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Schaffhausen</t>
+  </si>
+  <si>
+    <t>Olten</t>
   </si>
 </sst>
 </file>
@@ -277,6 +289,158 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>93.682000000000002</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="G3">
+            <v>128.465</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>156.2773333333333</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>206.8955</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>199.85633333333331</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>111.3966666666667</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="G8">
+            <v>285.65940079365078</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="G9">
+            <v>177.232</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="G10">
+            <v>162.97499999999999</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="G11">
+            <v>183.01900000000001</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="G12">
+            <v>174.678</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="G13">
+            <v>226.01750000000001</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="G14">
+            <v>113.53400000000001</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="G15">
+            <v>143.61799999999999</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="G16">
+            <v>230.31212500000001</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="G17">
+            <v>284.79578640776703</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="G18">
+            <v>222.78700000000001</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="G19">
+            <v>267.39850000000001</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="G20">
+            <v>264.07260000000002</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="G21">
+            <v>200.399</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="G22">
+            <v>244.66800000000001</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="G23">
+            <v>184.88050000000001</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="G24">
+            <v>184.49799999999999</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="G25">
+            <v>274.60050000000001</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="G26">
+            <v>130.041</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="G27">
+            <v>182.9846</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="G28">
+            <v>260.41075000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -586,15 +750,15 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -602,15 +766,15 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,20 +782,20 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -639,10 +803,162 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -657,34 +973,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -711,10 +1027,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -722,27 +1038,27 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C2">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C3">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -750,27 +1066,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
         <v>2</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -778,32 +1094,32 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -817,16 +1133,282 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>56</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
         <v>1442</v>
       </c>
-      <c r="D9">
+      <c r="D17">
         <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23">
+        <v>14</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>14</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>14</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27">
+        <v>35</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>56</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -836,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -859,34 +1441,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -894,24 +1476,26 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>2.8</v>
+        <f>E2/80</f>
+        <v>1.171</v>
       </c>
       <c r="E2">
-        <v>247.95599999999999</v>
+        <f>ROUND([1]Sheet1!G2,2)</f>
+        <v>93.68</v>
       </c>
       <c r="F2">
-        <f>L2+(50/1)</f>
-        <v>246.7296</v>
+        <f>L2+(K2/J2)</f>
+        <v>162.416</v>
       </c>
       <c r="G2">
-        <f>1.3*L2</f>
-        <v>255.74848000000003</v>
+        <f>1.3*F2</f>
+        <v>211.14080000000001</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -926,32 +1510,35 @@
         <v>50</v>
       </c>
       <c r="L2">
-        <v>196.7296</v>
+        <f>1.2*E2</f>
+        <v>112.41600000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>2.8</v>
+        <f t="shared" ref="D3:D28" si="0">E3/80</f>
+        <v>1.6058749999999999</v>
       </c>
       <c r="E3">
-        <v>245.02775</v>
+        <f>ROUND([1]Sheet1!G3,2)</f>
+        <v>128.47</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F17" si="0">L3+(50/1)</f>
-        <v>242.0444</v>
+        <f t="shared" ref="F3:F55" si="1">L3+(K3/J3)</f>
+        <v>204.16399999999999</v>
       </c>
       <c r="G3">
-        <f>1.3*L3</f>
-        <v>249.65772000000001</v>
+        <f t="shared" ref="G3:G28" si="2">1.3*F3</f>
+        <v>265.41320000000002</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -966,7 +1553,8 @@
         <v>50</v>
       </c>
       <c r="L3">
-        <v>192.0444</v>
+        <f t="shared" ref="L3:L28" si="3">1.2*E3</f>
+        <v>154.16399999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -974,24 +1562,26 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>2.86</v>
+        <f t="shared" si="0"/>
+        <v>1.9535</v>
       </c>
       <c r="E4">
-        <v>247.95599999999999</v>
+        <f>ROUND([1]Sheet1!G4,2)</f>
+        <v>156.28</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
-        <v>246.7296</v>
+        <f t="shared" si="1"/>
+        <v>237.536</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G9" si="1">1.3*L4</f>
-        <v>255.74848000000003</v>
+        <f t="shared" si="2"/>
+        <v>308.79680000000002</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1006,32 +1596,35 @@
         <v>50</v>
       </c>
       <c r="L4">
-        <v>196.7296</v>
+        <f t="shared" si="3"/>
+        <v>187.536</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>2.86</v>
+        <f t="shared" si="0"/>
+        <v>2.5862500000000002</v>
       </c>
       <c r="E5">
-        <v>245.02775</v>
+        <f>ROUND([1]Sheet1!G5,2)</f>
+        <v>206.9</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
-        <v>242.0444</v>
+        <f t="shared" si="1"/>
+        <v>298.27999999999997</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
-        <v>249.65772000000001</v>
+        <f t="shared" si="2"/>
+        <v>387.76399999999995</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1046,7 +1639,8 @@
         <v>50</v>
       </c>
       <c r="L5">
-        <v>192.0444</v>
+        <f t="shared" si="3"/>
+        <v>248.28</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -1054,24 +1648,26 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>2.5</v>
+        <f t="shared" si="0"/>
+        <v>2.4982500000000001</v>
       </c>
       <c r="E6">
-        <v>173.01300000000001</v>
+        <f>ROUND([1]Sheet1!G6,2)</f>
+        <v>199.86</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>226.82079999999999</v>
+        <f t="shared" si="1"/>
+        <v>289.83199999999999</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
-        <v>229.86704</v>
+        <f t="shared" si="2"/>
+        <v>376.78160000000003</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1086,32 +1682,35 @@
         <v>50</v>
       </c>
       <c r="L6">
-        <v>176.82079999999999</v>
+        <f t="shared" si="3"/>
+        <v>239.83199999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>2.5</v>
+        <f t="shared" si="0"/>
+        <v>1.3925000000000001</v>
       </c>
       <c r="E7">
-        <v>183.001</v>
+        <f>ROUND([1]Sheet1!G7,2)</f>
+        <v>111.4</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
-        <v>242.80160000000001</v>
+        <f t="shared" si="1"/>
+        <v>183.68</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
-        <v>250.64208000000002</v>
+        <f t="shared" si="2"/>
+        <v>238.78400000000002</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1126,32 +1725,35 @@
         <v>50</v>
       </c>
       <c r="L7">
-        <v>192.80160000000001</v>
+        <f t="shared" si="3"/>
+        <v>133.68</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>3.25</v>
+        <f t="shared" si="0"/>
+        <v>3.5707500000000003</v>
       </c>
       <c r="E8">
-        <v>285.77073015873009</v>
+        <f>ROUND([1]Sheet1!G8,2)</f>
+        <v>285.66000000000003</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
-        <v>307.23316825396802</v>
+        <f t="shared" si="1"/>
+        <v>392.79200000000003</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>334.40311873015844</v>
+        <f t="shared" si="2"/>
+        <v>510.62960000000004</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1166,32 +1768,35 @@
         <v>50</v>
       </c>
       <c r="L8">
-        <v>257.23316825396802</v>
+        <f t="shared" si="3"/>
+        <v>342.79200000000003</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>3.25</v>
+        <f t="shared" si="0"/>
+        <v>2.2153749999999999</v>
       </c>
       <c r="E9">
-        <v>284.86388834951458</v>
+        <f>ROUND([1]Sheet1!G9,2)</f>
+        <v>177.23</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
-        <v>305.782221359223</v>
+        <f t="shared" si="1"/>
+        <v>262.67599999999999</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
-        <v>332.5168877669899</v>
+        <f t="shared" si="2"/>
+        <v>341.47879999999998</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1206,287 +1811,309 @@
         <v>50</v>
       </c>
       <c r="L9">
-        <v>255.782221359223</v>
+        <f t="shared" si="3"/>
+        <v>212.67599999999999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
-        <v>3</v>
-      </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>2.909322916666667</v>
+        <f t="shared" si="0"/>
+        <v>2.0372499999999998</v>
       </c>
       <c r="E10">
-        <v>247.95599999999999</v>
+        <f>ROUND([1]Sheet1!G10,2)</f>
+        <v>162.97999999999999</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
-        <v>205.63758000000001</v>
+        <f t="shared" si="1"/>
+        <v>245.57599999999999</v>
       </c>
       <c r="G10">
-        <f>1.6*L10</f>
-        <v>249.02012800000003</v>
+        <f t="shared" si="2"/>
+        <v>319.24880000000002</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2000</v>
+      </c>
+      <c r="J10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>80</v>
-      </c>
       <c r="K10">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L10">
-        <v>155.63758000000001</v>
+        <f t="shared" si="3"/>
+        <v>195.57599999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>2.909322916666667</v>
+        <f t="shared" si="0"/>
+        <v>2.28775</v>
       </c>
       <c r="E11">
-        <v>245.02775</v>
+        <f>ROUND([1]Sheet1!G11,2)</f>
+        <v>183.02</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
-        <v>205.47652625000001</v>
+        <f t="shared" si="1"/>
+        <v>269.62400000000002</v>
       </c>
       <c r="G11">
-        <f t="shared" ref="G11:G17" si="2">1.6*L11</f>
-        <v>248.76244200000002</v>
+        <f t="shared" si="2"/>
+        <v>350.51120000000003</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>2000</v>
+      </c>
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <v>80</v>
-      </c>
       <c r="K11">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>155.47652625000001</v>
+        <f t="shared" si="3"/>
+        <v>219.624</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>2.9274470899470901</v>
+        <f t="shared" si="0"/>
+        <v>2.1835</v>
       </c>
       <c r="E12">
-        <v>247.95599999999999</v>
+        <f>ROUND([1]Sheet1!G12,2)</f>
+        <v>174.68</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
-        <v>205.63758000000001</v>
+        <f t="shared" si="1"/>
+        <v>259.61599999999999</v>
       </c>
       <c r="G12">
         <f t="shared" si="2"/>
-        <v>249.02012800000003</v>
+        <v>337.50079999999997</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2000</v>
+      </c>
+      <c r="J12">
         <v>1</v>
       </c>
-      <c r="I12">
-        <v>3</v>
-      </c>
-      <c r="J12">
-        <v>80</v>
-      </c>
       <c r="K12">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L12">
-        <v>155.63758000000001</v>
+        <f t="shared" si="3"/>
+        <v>209.61600000000001</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>2.9274470899470901</v>
+        <f t="shared" si="0"/>
+        <v>2.82525</v>
       </c>
       <c r="E13">
-        <v>245.02775</v>
+        <f>ROUND([1]Sheet1!G13,2)</f>
+        <v>226.02</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
-        <v>205.47652625000001</v>
+        <f t="shared" si="1"/>
+        <v>321.22399999999999</v>
       </c>
       <c r="G13">
         <f t="shared" si="2"/>
-        <v>248.76244200000002</v>
+        <v>417.59120000000001</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2000</v>
+      </c>
+      <c r="J13">
         <v>1</v>
       </c>
-      <c r="I13">
-        <v>3</v>
-      </c>
-      <c r="J13">
-        <v>80</v>
-      </c>
       <c r="K13">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L13">
-        <v>155.47652625000001</v>
+        <f t="shared" si="3"/>
+        <v>271.22399999999999</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
         <v>2</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>3.1249691358024689</v>
+        <f t="shared" si="0"/>
+        <v>1.419125</v>
       </c>
       <c r="E14">
-        <v>173.01300000000001</v>
+        <f>ROUND([1]Sheet1!G14,2)</f>
+        <v>113.53</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
-        <v>201.515715</v>
+        <f t="shared" si="1"/>
+        <v>186.23599999999999</v>
       </c>
       <c r="G14">
         <f t="shared" si="2"/>
-        <v>242.42514400000002</v>
+        <v>242.10679999999999</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2000</v>
+      </c>
+      <c r="J14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <v>80</v>
-      </c>
       <c r="K14">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L14">
-        <v>151.515715</v>
+        <f t="shared" si="3"/>
+        <v>136.23599999999999</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>2.7516269841269838</v>
+        <f t="shared" si="0"/>
+        <v>1.79525</v>
       </c>
       <c r="E15">
-        <v>183.001</v>
+        <f>ROUND([1]Sheet1!G15,2)</f>
+        <v>143.62</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
-        <v>202.065055</v>
+        <f t="shared" si="1"/>
+        <v>222.34399999999999</v>
       </c>
       <c r="G15">
         <f t="shared" si="2"/>
-        <v>243.30408800000001</v>
+        <v>289.04719999999998</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2000</v>
+      </c>
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
-      <c r="J15">
-        <v>80</v>
-      </c>
       <c r="K15">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L15">
-        <v>152.065055</v>
+        <f t="shared" si="3"/>
+        <v>172.34399999999999</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>3.147626763668431</v>
+        <f t="shared" si="0"/>
+        <v>2.8788749999999999</v>
       </c>
       <c r="E16">
-        <v>285.77073015873009</v>
+        <f>ROUND([1]Sheet1!G16,2)</f>
+        <v>230.31</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
-        <v>207.71739015873021</v>
+        <f t="shared" si="1"/>
+        <v>326.37200000000001</v>
       </c>
       <c r="G16">
         <f t="shared" si="2"/>
-        <v>252.34782425396835</v>
+        <v>424.28360000000004</v>
       </c>
       <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>2000</v>
+      </c>
+      <c r="J16">
         <v>1</v>
       </c>
-      <c r="I16">
-        <v>3</v>
-      </c>
-      <c r="J16">
-        <v>80</v>
-      </c>
       <c r="K16">
-        <v>4000</v>
+        <v>50</v>
       </c>
       <c r="L16">
-        <v>157.71739015873021</v>
+        <f t="shared" si="3"/>
+        <v>276.37200000000001</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1494,39 +2121,1649 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>3.169861111111111</v>
+        <f t="shared" si="0"/>
+        <v>3.56</v>
       </c>
       <c r="E17">
-        <v>284.86388834951458</v>
+        <f>ROUND([1]Sheet1!G17,2)</f>
+        <v>284.8</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
-        <v>207.66751385922331</v>
+        <f t="shared" si="1"/>
+        <v>391.76</v>
       </c>
       <c r="G17">
         <f t="shared" si="2"/>
-        <v>252.26802217475731</v>
+        <v>509.28800000000001</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>2000</v>
+      </c>
+      <c r="J17">
         <v>1</v>
       </c>
-      <c r="I17">
+      <c r="K17">
+        <v>50</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>341.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="J17">
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>2.784875</v>
+      </c>
+      <c r="E18">
+        <f>ROUND([1]Sheet1!G18,2)</f>
+        <v>222.79</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>317.34799999999996</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>412.55239999999998</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>2000</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>50</v>
+      </c>
+      <c r="L18">
+        <f>1.2*E18</f>
+        <v>267.34799999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>3.3424999999999998</v>
+      </c>
+      <c r="E19">
+        <f>ROUND([1]Sheet1!G19,2)</f>
+        <v>267.39999999999998</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>370.87999999999994</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>482.14399999999995</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>2000</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>50</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>320.87999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>3.300875</v>
+      </c>
+      <c r="E20">
+        <f>ROUND([1]Sheet1!G20,2)</f>
+        <v>264.07</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>366.88399999999996</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>476.94919999999996</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>2000</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>50</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>316.88399999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="E21">
+        <f>ROUND([1]Sheet1!G21,2)</f>
+        <v>200.4</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>290.48</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>377.62400000000002</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>2000</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>50</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>240.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>3.0583749999999998</v>
+      </c>
+      <c r="E22">
+        <f>ROUND([1]Sheet1!G22,2)</f>
+        <v>244.67</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>343.60399999999998</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>446.68520000000001</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>2000</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>50</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>293.60399999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>2.3109999999999999</v>
+      </c>
+      <c r="E23">
+        <f>ROUND([1]Sheet1!G23,2)</f>
+        <v>184.88</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>271.85599999999999</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>353.4128</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2000</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>50</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>221.85599999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>2.3062499999999999</v>
+      </c>
+      <c r="E24">
+        <f>ROUND([1]Sheet1!G24,2)</f>
+        <v>184.5</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>271.39999999999998</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>352.82</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>2000</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>50</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>221.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>3.4325000000000001</v>
+      </c>
+      <c r="E25">
+        <f>ROUND([1]Sheet1!G25,2)</f>
+        <v>274.60000000000002</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>379.52000000000004</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="2"/>
+        <v>493.37600000000009</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>2000</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>50</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>329.52000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>1.6254999999999999</v>
+      </c>
+      <c r="E26">
+        <f>ROUND([1]Sheet1!G26,2)</f>
+        <v>130.04</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>206.04799999999997</v>
+      </c>
+      <c r="G26">
+        <f>1.3*F26</f>
+        <v>267.86239999999998</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>2000</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>50</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>156.04799999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>2.2872499999999998</v>
+      </c>
+      <c r="E27">
+        <f>ROUND([1]Sheet1!G27,2)</f>
+        <v>182.98</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>269.57600000000002</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="2"/>
+        <v>350.44880000000006</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>2000</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>50</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>219.57599999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>3.2551250000000005</v>
+      </c>
+      <c r="E28">
+        <f>ROUND([1]Sheet1!G28,2)</f>
+        <v>260.41000000000003</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>362.49200000000002</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="2"/>
+        <v>471.23960000000005</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>2000</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>50</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>312.49200000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <f>E29/120</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="E29">
+        <v>81</v>
+      </c>
+      <c r="F29">
+        <f>L29+(K29/J29)</f>
+        <v>131</v>
+      </c>
+      <c r="G29">
+        <f xml:space="preserve"> 1.6*F29</f>
+        <v>209.60000000000002</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29">
         <v>80</v>
       </c>
-      <c r="K17">
+      <c r="K29">
         <v>4000</v>
       </c>
-      <c r="L17">
-        <v>157.66751385922331</v>
+      <c r="L29">
+        <f>E29</f>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:D55" si="4">E30/120</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E30">
+        <v>95</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="G30">
+        <f t="shared" ref="G30:G55" si="5" xml:space="preserve"> 1.6*F30</f>
+        <v>232</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>80</v>
+      </c>
+      <c r="K30">
+        <v>4000</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ref="L30:L55" si="6">E30</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="4"/>
+        <v>1.4416666666666667</v>
+      </c>
+      <c r="E31">
+        <v>173</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="5"/>
+        <v>356.8</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>80</v>
+      </c>
+      <c r="K31">
+        <v>4000</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="6"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="4"/>
+        <v>1.8416666666666666</v>
+      </c>
+      <c r="E32">
+        <v>221</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>271</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="5"/>
+        <v>433.6</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>80</v>
+      </c>
+      <c r="K32">
+        <v>4000</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="6"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="4"/>
+        <v>1.3416666666666666</v>
+      </c>
+      <c r="E33">
+        <v>161</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>211</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="5"/>
+        <v>337.6</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>80</v>
+      </c>
+      <c r="K33">
+        <v>4000</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="6"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="4"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E34">
+        <v>65</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>3</v>
+      </c>
+      <c r="J34">
+        <v>80</v>
+      </c>
+      <c r="K34">
+        <v>4000</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="6"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="4"/>
+        <v>2.2583333333333333</v>
+      </c>
+      <c r="E35">
+        <v>271</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>321</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="5"/>
+        <v>513.6</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <v>80</v>
+      </c>
+      <c r="K35">
+        <v>4000</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="6"/>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="4"/>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E36">
+        <v>93</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="5"/>
+        <v>228.8</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>80</v>
+      </c>
+      <c r="K36">
+        <v>4000</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="6"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="4"/>
+        <v>1.4416666666666667</v>
+      </c>
+      <c r="E37">
+        <v>173</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>223</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="5"/>
+        <v>356.8</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>80</v>
+      </c>
+      <c r="K37">
+        <v>4000</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="6"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="4"/>
+        <v>1.6083333333333334</v>
+      </c>
+      <c r="E38">
+        <v>193</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>243</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="5"/>
+        <v>388.8</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>80</v>
+      </c>
+      <c r="K38">
+        <v>4000</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="6"/>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="4"/>
+        <v>1.5416666666666667</v>
+      </c>
+      <c r="E39">
+        <v>185</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>235</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="5"/>
+        <v>376</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>80</v>
+      </c>
+      <c r="K39">
+        <v>4000</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="6"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="4"/>
+        <v>1.9583333333333333</v>
+      </c>
+      <c r="E40">
+        <v>235</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>285</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="5"/>
+        <v>456</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>80</v>
+      </c>
+      <c r="K40">
+        <v>4000</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="6"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="4"/>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E41">
+        <v>95</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="5"/>
+        <v>232</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>80</v>
+      </c>
+      <c r="K41">
+        <v>4000</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="6"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="4"/>
+        <v>1.1333333333333333</v>
+      </c>
+      <c r="E42">
+        <v>136</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="5"/>
+        <v>297.60000000000002</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>80</v>
+      </c>
+      <c r="K42">
+        <v>4000</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="6"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="4"/>
+        <v>1.8416666666666666</v>
+      </c>
+      <c r="E43">
+        <v>221</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>271</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="5"/>
+        <v>433.6</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>80</v>
+      </c>
+      <c r="K43">
+        <v>4000</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="6"/>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="4"/>
+        <v>2.2583333333333333</v>
+      </c>
+      <c r="E44">
+        <v>271</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>321</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="5"/>
+        <v>513.6</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>80</v>
+      </c>
+      <c r="K44">
+        <v>4000</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="6"/>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="4"/>
+        <v>1.9583333333333333</v>
+      </c>
+      <c r="E45">
+        <v>235</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>285</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="5"/>
+        <v>456</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>80</v>
+      </c>
+      <c r="K45">
+        <v>4000</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="6"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="4"/>
+        <v>2.1416666666666666</v>
+      </c>
+      <c r="E46">
+        <v>257</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>307</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="5"/>
+        <v>491.20000000000005</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>80</v>
+      </c>
+      <c r="K46">
+        <v>4000</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="6"/>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="4"/>
+        <v>1.8916666666666666</v>
+      </c>
+      <c r="E47">
+        <v>227</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>277</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="5"/>
+        <v>443.20000000000005</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>80</v>
+      </c>
+      <c r="K47">
+        <v>4000</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="6"/>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="4"/>
+        <v>1.3416666666666666</v>
+      </c>
+      <c r="E48">
+        <v>161</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>211</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="5"/>
+        <v>337.6</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>80</v>
+      </c>
+      <c r="K48">
+        <v>4000</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="6"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="4"/>
+        <v>1.5583333333333333</v>
+      </c>
+      <c r="E49">
+        <v>187</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>237</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="5"/>
+        <v>379.20000000000005</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>80</v>
+      </c>
+      <c r="K49">
+        <v>4000</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="6"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="4"/>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E50">
+        <v>93</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="5"/>
+        <v>228.8</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+      <c r="J50">
+        <v>80</v>
+      </c>
+      <c r="K50">
+        <v>4000</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="6"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="4"/>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="E51">
+        <v>153</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>203</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="5"/>
+        <v>324.8</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>80</v>
+      </c>
+      <c r="K51">
+        <v>4000</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="6"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="4"/>
+        <v>2.7833333333333332</v>
+      </c>
+      <c r="E52">
+        <v>334</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="5"/>
+        <v>614.40000000000009</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>3</v>
+      </c>
+      <c r="J52">
+        <v>80</v>
+      </c>
+      <c r="K52">
+        <v>4000</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="6"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="4"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E53">
+        <v>65</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="5"/>
+        <v>184</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53">
+        <v>80</v>
+      </c>
+      <c r="K53">
+        <v>4000</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="6"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="4"/>
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="E54">
+        <v>106</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="5"/>
+        <v>249.60000000000002</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>3</v>
+      </c>
+      <c r="J54">
+        <v>80</v>
+      </c>
+      <c r="K54">
+        <v>4000</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="6"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="4"/>
+        <v>1.8916666666666666</v>
+      </c>
+      <c r="E55">
+        <v>227</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>277</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="5"/>
+        <v>443.20000000000005</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>80</v>
+      </c>
+      <c r="K55">
+        <v>4000</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="6"/>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -1541,30 +3778,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>-0.3422</v>
@@ -1587,7 +3824,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>-3.9592000000000001</v>
@@ -1610,7 +3847,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>-0.2359</v>
@@ -1633,7 +3870,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>-4.8800000000000003E-2</v>
@@ -1656,7 +3893,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>0.80410000000000004</v>
@@ -1679,7 +3916,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B7">
         <v>0.15820000000000001</v>
@@ -1721,25 +3958,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1747,7 +3984,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>-0.3422</v>
@@ -1762,7 +3999,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G2">
-        <v>0.27838088829549701</v>
+        <v>0.41757133244324551</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1770,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1785,7 +4022,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G3">
-        <v>0.27838088829549701</v>
+        <v>0.41757133244324551</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1793,7 +4030,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>-0.3422</v>
@@ -1808,7 +4045,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G4">
-        <v>0.19117356776814501</v>
+        <v>0.28676035165221753</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1816,7 +4053,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1831,7 +4068,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G5">
-        <v>0.19117356776814501</v>
+        <v>0.28676035165221753</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1839,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>-0.3422</v>
@@ -1854,7 +4091,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G6">
-        <v>0.16200582133621699</v>
+        <v>0.24300873200432549</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1862,7 +4099,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1877,7 +4114,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G7">
-        <v>0.16200582133621699</v>
+        <v>0.24300873200432549</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1885,7 +4122,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>-0.3422</v>
@@ -1900,7 +4137,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G8">
-        <v>0.136668886034159</v>
+        <v>0.2050033290512385</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1908,7 +4145,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1923,7 +4160,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G9">
-        <v>0.136668886034159</v>
+        <v>0.2050033290512385</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1931,7 +4168,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>-0.3422</v>
@@ -1946,7 +4183,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G10">
-        <v>0.106997365635085</v>
+        <v>0.16049604845262749</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1954,7 +4191,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1969,7 +4206,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G11">
-        <v>0.106997365635085</v>
+        <v>0.16049604845262749</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1977,7 +4214,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>-0.3422</v>
@@ -1992,7 +4229,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G12">
-        <v>0.234706653372145</v>
+        <v>0.35205998005821748</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2000,7 +4237,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2015,7 +4252,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G13">
-        <v>0.234706653372145</v>
+        <v>0.35205998005821748</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2023,7 +4260,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>-0.3422</v>
@@ -2038,7 +4275,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G14">
-        <v>0.18449635759480501</v>
+        <v>0.27674453639220753</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2046,7 +4283,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2061,7 +4298,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G15">
-        <v>0.18449635759480501</v>
+        <v>0.27674453639220753</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2069,13 +4306,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>-0.3422</v>
       </c>
       <c r="D16">
-        <v>-1.50967534831115E-2</v>
+        <v>-1.5096753483111501E-2</v>
       </c>
       <c r="E16">
         <v>-2.4015859146499299E-2</v>
@@ -2084,7 +4321,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G16">
-        <v>0.15690002641624901</v>
+        <v>0.23535003962437351</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2092,13 +4329,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>-1.50967534831115E-2</v>
+        <v>-1.5096753483111501E-2</v>
       </c>
       <c r="E17">
         <v>-2.4015859146499299E-2</v>
@@ -2107,7 +4344,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G17">
-        <v>0.15690002641624901</v>
+        <v>0.23535003962437351</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2115,7 +4352,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>-0.3422</v>
@@ -2130,7 +4367,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G18">
-        <v>0.13139107817918899</v>
+        <v>0.19708661726878349</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2138,7 +4375,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2153,7 +4390,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G19">
-        <v>0.13139107817918899</v>
+        <v>0.19708661726878349</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2161,7 +4398,7 @@
         <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>-0.3422</v>
@@ -2176,7 +4413,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G20">
-        <v>9.92137122552217E-2</v>
+        <v>0.14882056838283256</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2184,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2199,7 +4436,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G21">
-        <v>9.92137122552217E-2</v>
+        <v>0.14882056838283256</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2207,13 +4444,13 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>-0.3422</v>
       </c>
       <c r="D22">
-        <v>-0.249153673764685</v>
+        <v>-0.24915367376468503</v>
       </c>
       <c r="E22">
         <v>-3.8468993238358701E-2</v>
@@ -2222,7 +4459,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G22">
-        <v>0.21857165259960801</v>
+        <v>0.32785747889941202</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -2230,13 +4467,13 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>-0.249153673764685</v>
+        <v>-0.24915367376468503</v>
       </c>
       <c r="E23">
         <v>-3.8468993238358701E-2</v>
@@ -2245,7 +4482,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G23">
-        <v>0.21857165259960801</v>
+        <v>0.32785747889941202</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2253,7 +4490,7 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>-0.3422</v>
@@ -2268,7 +4505,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G24">
-        <v>0.17838490366929899</v>
+        <v>0.26757735550394846</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2276,7 +4513,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2291,7 +4528,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G25">
-        <v>0.17838490366929899</v>
+        <v>0.26757735550394846</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2299,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>-0.3422</v>
@@ -2314,7 +4551,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G26">
-        <v>0.15186536405861401</v>
+        <v>0.22779804608792101</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2322,7 +4559,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2337,7 +4574,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G27">
-        <v>0.15186536405861401</v>
+        <v>0.22779804608792101</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2345,7 +4582,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>-0.3422</v>
@@ -2360,7 +4597,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G28">
-        <v>0.125896766033716</v>
+        <v>0.18884514905057398</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2368,7 +4605,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2383,7 +4620,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G29">
-        <v>0.125896766033716</v>
+        <v>0.18884514905057398</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2391,7 +4628,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>-0.3422</v>
@@ -2406,7 +4643,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G30">
-        <v>8.9951134108337202E-2</v>
+        <v>0.1349267011625058</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2414,7 +4651,7 @@
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2429,7 +4666,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G31">
-        <v>8.9951134108337202E-2</v>
+        <v>0.1349267011625058</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2437,7 +4674,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>-0.3422</v>
@@ -2452,7 +4689,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G32">
-        <v>0.207488331847902</v>
+        <v>0.31123249777185302</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2460,7 +4697,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2475,7 +4712,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G33">
-        <v>0.207488331847902</v>
+        <v>0.31123249777185302</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2483,7 +4720,7 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>-0.3422</v>
@@ -2498,7 +4735,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G34">
-        <v>0.17267144014616601</v>
+        <v>0.25900716021924902</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2506,7 +4743,7 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2521,7 +4758,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G35">
-        <v>0.17267144014616601</v>
+        <v>0.25900716021924902</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2529,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36">
         <v>-0.3422</v>
@@ -2544,7 +4781,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G36">
-        <v>0.14684959159223601</v>
+        <v>0.22027438738835403</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2552,7 +4789,7 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2567,7 +4804,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G37">
-        <v>0.14684959159223601</v>
+        <v>0.22027438738835403</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2575,7 +4812,7 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>-0.3422</v>
@@ -2590,7 +4827,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G38">
-        <v>0.12009401002820801</v>
+        <v>0.180141015042312</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2598,7 +4835,7 @@
         <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2613,7 +4850,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G39">
-        <v>0.12009401002820801</v>
+        <v>0.180141015042312</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2621,7 +4858,7 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40">
         <v>-0.3422</v>
@@ -2636,7 +4873,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G40">
-        <v>7.7981014339295607E-2</v>
+        <v>0.11697152150894341</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2644,7 +4881,7 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2659,7 +4896,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G41">
-        <v>7.7981014339295607E-2</v>
+        <v>0.11697152150894341</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2667,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>-0.3422</v>
@@ -2682,7 +4919,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G42">
-        <v>0.19868152870184899</v>
+        <v>0.2980222930527735</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2690,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2705,7 +4942,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G43">
-        <v>0.19868152870184899</v>
+        <v>0.2980222930527735</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2713,7 +4950,7 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44">
         <v>-0.3422</v>
@@ -2728,7 +4965,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G44">
-        <v>0.16724031476746901</v>
+        <v>0.2508604721512035</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2736,7 +4973,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2751,7 +4988,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G45">
-        <v>0.16724031476746901</v>
+        <v>0.2508604721512035</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2759,7 +4996,7 @@
         <v>23</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46">
         <v>-0.3422</v>
@@ -2774,7 +5011,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G46">
-        <v>0.14180183277015301</v>
+        <v>0.21270274915522952</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2782,7 +5019,7 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2797,7 +5034,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G47">
-        <v>0.14180183277015301</v>
+        <v>0.21270274915522952</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2805,13 +5042,13 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <v>-0.3422</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>51</v>
+      <c r="D48" s="2">
+        <v>0.109726907819878</v>
       </c>
       <c r="E48">
         <v>-5.9890316597160403E-2</v>
@@ -2820,7 +5057,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G48">
-        <v>0.113856519837811</v>
+        <v>0.17078477975671652</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2828,13 +5065,13 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>51</v>
+      <c r="D49" s="2">
+        <v>0.109726907819878</v>
       </c>
       <c r="E49">
         <v>-5.9890316597160403E-2</v>
@@ -2843,7 +5080,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G49">
-        <v>0.113856519837811</v>
+        <v>0.17078477975671652</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2851,7 +5088,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C50">
         <v>-0.3422</v>
@@ -2866,7 +5103,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G50">
-        <v>5.9326707131112301E-2</v>
+        <v>8.8990060696668455E-2</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2874,7 +5111,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2889,7 +5126,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G51">
-        <v>5.9326707131112301E-2</v>
+        <v>8.8990060696668455E-2</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2897,7 +5134,7 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52">
         <v>-0.3422</v>
@@ -2912,7 +5149,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G52">
-        <v>0.26113206276743001</v>
+        <v>0.39169809415114498</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2920,7 +5157,7 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2935,7 +5172,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G53">
-        <v>0.26113206276743001</v>
+        <v>0.39169809415114498</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2943,7 +5180,7 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54">
         <v>-0.3422</v>
@@ -2958,7 +5195,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G54">
-        <v>0.18978211267133499</v>
+        <v>0.28467316900700246</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2966,7 +5203,7 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2981,7 +5218,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G55">
-        <v>0.18978211267133499</v>
+        <v>0.28467316900700246</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2989,7 +5226,7 @@
         <v>28</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56">
         <v>-0.3422</v>
@@ -3004,7 +5241,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G56">
-        <v>0.160976321100675</v>
+        <v>0.2414644816510125</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -3012,7 +5249,7 @@
         <v>28</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3027,7 +5264,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G57">
-        <v>0.160976321100675</v>
+        <v>0.2414644816510125</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -3035,7 +5272,7 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58">
         <v>-0.3422</v>
@@ -3050,7 +5287,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G58">
-        <v>0.135626991811719</v>
+        <v>0.2034404877175785</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -3058,7 +5295,7 @@
         <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -3073,7 +5310,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G59">
-        <v>0.135626991811719</v>
+        <v>0.2034404877175785</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -3081,7 +5318,7 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60">
         <v>-0.3422</v>
@@ -3096,7 +5333,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G60">
-        <v>0.10552738054232</v>
+        <v>0.15829107081347998</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -3104,7 +5341,7 @@
         <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3119,7 +5356,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G61">
-        <v>0.10552738054232</v>
+        <v>0.15829107081347998</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -3127,7 +5364,7 @@
         <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62">
         <v>-0.3422</v>
@@ -3142,7 +5379,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G62">
-        <v>0.23076632680604101</v>
+        <v>0.34614949020906149</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -3150,7 +5387,7 @@
         <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3165,7 +5402,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G63">
-        <v>0.23076632680604101</v>
+        <v>0.34614949020906149</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -3173,7 +5410,7 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C64">
         <v>-0.3422</v>
@@ -3188,7 +5425,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G64">
-        <v>0.18323518709658501</v>
+        <v>0.2748527806448775</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3196,7 +5433,7 @@
         <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3211,7 +5448,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G65">
-        <v>0.18323518709658501</v>
+        <v>0.2748527806448775</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3219,7 +5456,7 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66">
         <v>-0.3422</v>
@@ -3234,7 +5471,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G66">
-        <v>0.15588912474738201</v>
+        <v>0.233833687121073</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3242,7 +5479,7 @@
         <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3257,7 +5494,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G67">
-        <v>0.15588912474738201</v>
+        <v>0.233833687121073</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3265,7 +5502,7 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68">
         <v>-0.3422</v>
@@ -3280,7 +5517,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G68">
-        <v>0.130312119260098</v>
+        <v>0.195468178890147</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -3288,7 +5525,7 @@
         <v>34</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3303,7 +5540,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G69">
-        <v>0.130312119260098</v>
+        <v>0.195468178890147</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3311,7 +5548,7 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70">
         <v>-0.3422</v>
@@ -3326,7 +5563,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G70">
-        <v>9.7504555078177901E-2</v>
+        <v>0.14625683261726685</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -3334,7 +5571,7 @@
         <v>35</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3349,7 +5586,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G71">
-        <v>9.7504555078177901E-2</v>
+        <v>0.14625683261726685</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -3357,7 +5594,7 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72">
         <v>-0.3422</v>
@@ -3372,7 +5609,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G72">
-        <v>0.21608921316579399</v>
+        <v>0.32413381974869099</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -3380,7 +5617,7 @@
         <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3395,7 +5632,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G73">
-        <v>0.21608921316579399</v>
+        <v>0.32413381974869099</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -3403,7 +5640,7 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74">
         <v>-0.3422</v>
@@ -3418,7 +5655,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G74">
-        <v>0.17721464005632301</v>
+        <v>0.2658219600844845</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3426,7 +5663,7 @@
         <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3441,7 +5678,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G75">
-        <v>0.17721464005632301</v>
+        <v>0.2658219600844845</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3449,7 +5686,7 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76">
         <v>-0.3422</v>
@@ -3464,7 +5701,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G76">
-        <v>0.150862322872827</v>
+        <v>0.22629348430924051</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -3472,7 +5709,7 @@
         <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3487,7 +5724,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G77">
-        <v>0.150862322872827</v>
+        <v>0.22629348430924051</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3495,7 +5732,7 @@
         <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78">
         <v>-0.3422</v>
@@ -3510,7 +5747,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G78">
-        <v>0.124764319466211</v>
+        <v>0.18714647919931648</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3518,7 +5755,7 @@
         <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3533,7 +5770,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G79">
-        <v>0.124764319466211</v>
+        <v>0.18714647919931648</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -3541,7 +5778,7 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80">
         <v>-0.3422</v>
@@ -3556,7 +5793,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G80">
-        <v>8.78353659127772E-2</v>
+        <v>0.13175304886916581</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -3564,7 +5801,7 @@
         <v>40</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3579,7 +5816,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G81">
-        <v>8.78353659127772E-2</v>
+        <v>0.13175304886916581</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3587,7 +5824,7 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82">
         <v>-0.3422</v>
@@ -3602,7 +5839,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G82">
-        <v>0.20558815747089501</v>
+        <v>0.30838223620634253</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3610,7 +5847,7 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3625,7 +5862,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G83">
-        <v>0.20558815747089501</v>
+        <v>0.30838223620634253</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3633,7 +5870,7 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84">
         <v>-0.3422</v>
@@ -3648,7 +5885,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G84">
-        <v>0.17156570495913601</v>
+        <v>0.257348557438704</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3656,7 +5893,7 @@
         <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3671,7 +5908,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G85">
-        <v>0.17156570495913601</v>
+        <v>0.257348557438704</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3679,7 +5916,7 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86">
         <v>-0.3422</v>
@@ -3694,7 +5931,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G86">
-        <v>0.145844243784715</v>
+        <v>0.2187663656770725</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3702,7 +5939,7 @@
         <v>43</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3717,7 +5954,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G87">
-        <v>0.145844243784715</v>
+        <v>0.2187663656770725</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3725,13 +5962,13 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88">
         <v>-0.3422</v>
       </c>
       <c r="D88">
-        <v>-0.12219226888321</v>
+        <v>-0.12219226888320998</v>
       </c>
       <c r="E88">
         <v>-1.66189981816444E-2</v>
@@ -3740,7 +5977,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G88">
-        <v>0.118886169610286</v>
+        <v>0.17832925441542902</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3748,13 +5985,13 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>-0.12219226888321</v>
+        <v>-0.12219226888320998</v>
       </c>
       <c r="E89">
         <v>-1.66189981816444E-2</v>
@@ -3763,7 +6000,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G89">
-        <v>0.118886169610286</v>
+        <v>0.17832925441542902</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3771,7 +6008,7 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90">
         <v>-0.3422</v>
@@ -3786,7 +6023,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G90">
-        <v>7.5028091960408702E-2</v>
+        <v>0.11254213794061305</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3794,7 +6031,7 @@
         <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3809,7 +6046,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G91">
-        <v>7.5028091960408702E-2</v>
+        <v>0.11254213794061305</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3817,7 +6054,7 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92">
         <v>-0.3422</v>
@@ -3832,7 +6069,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G92">
-        <v>0.19709537499527699</v>
+        <v>0.2956430624929155</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3840,7 +6077,7 @@
         <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3855,7 +6092,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G93">
-        <v>0.19709537499527699</v>
+        <v>0.2956430624929155</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3863,7 +6100,7 @@
         <v>47</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94">
         <v>-0.3422</v>
@@ -3878,7 +6115,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G94">
-        <v>0.16618005863617699</v>
+        <v>0.24927008795426547</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3886,7 +6123,7 @@
         <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3901,7 +6138,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G95">
-        <v>0.16618005863617699</v>
+        <v>0.24927008795426547</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -3909,7 +6146,7 @@
         <v>48</v>
       </c>
       <c r="B96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C96">
         <v>-0.3422</v>
@@ -3924,7 +6161,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G96">
-        <v>0.140783845432841</v>
+        <v>0.21117576814926151</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3932,7 +6169,7 @@
         <v>48</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -3947,7 +6184,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G97">
-        <v>0.140783845432841</v>
+        <v>0.21117576814926151</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -3955,7 +6192,7 @@
         <v>49</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98">
         <v>-0.3422</v>
@@ -3970,7 +6207,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G98">
-        <v>0.112541935703094</v>
+        <v>0.16881290355464099</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3978,7 +6215,7 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3993,7 +6230,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G99">
-        <v>0.112541935703094</v>
+        <v>0.16881290355464099</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -4001,7 +6238,7 @@
         <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100">
         <v>-0.3422</v>
@@ -4016,7 +6253,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G100">
-        <v>5.3561732803062201E-2</v>
+        <v>8.0342599204593301E-2</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -4024,7 +6261,7 @@
         <v>50</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4039,7 +6276,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G101">
-        <v>5.3561732803062201E-2</v>
+        <v>8.0342599204593301E-2</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -4047,13 +6284,13 @@
         <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102">
         <v>-0.3422</v>
       </c>
       <c r="D102">
-        <v>-0.24009233438658201</v>
+        <v>-0.24009233438658203</v>
       </c>
       <c r="E102">
         <v>-5.9196738203285602E-2</v>
@@ -4062,7 +6299,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G102">
-        <v>0.25155739186431397</v>
+        <v>0.37733608779647099</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -4070,13 +6307,13 @@
         <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>-0.24009233438658201</v>
+        <v>-0.24009233438658203</v>
       </c>
       <c r="E103">
         <v>-5.9196738203285602E-2</v>
@@ -4085,7 +6322,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G103">
-        <v>0.25155739186431397</v>
+        <v>0.37733608779647099</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -4093,7 +6330,7 @@
         <v>52</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104">
         <v>-0.3422</v>
@@ -4108,7 +6345,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G104">
-        <v>0.188420806543214</v>
+        <v>0.28263120981482098</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -4116,7 +6353,7 @@
         <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4131,7 +6368,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G105">
-        <v>0.188420806543214</v>
+        <v>0.28263120981482098</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -4139,7 +6376,7 @@
         <v>53</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106">
         <v>-0.3422</v>
@@ -4154,7 +6391,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G106">
-        <v>0.159951453813239</v>
+        <v>0.2399271807198585</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -4162,7 +6399,7 @@
         <v>53</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4177,7 +6414,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G107">
-        <v>0.159951453813239</v>
+        <v>0.2399271807198585</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -4185,7 +6422,7 @@
         <v>54</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108">
         <v>-0.3422</v>
@@ -4200,7 +6437,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G108">
-        <v>0.13457881826043799</v>
+        <v>0.20186822739065699</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -4208,7 +6445,7 @@
         <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4223,7 +6460,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G109">
-        <v>0.13457881826043799</v>
+        <v>0.20186822739065699</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -4231,7 +6468,7 @@
         <v>55</v>
       </c>
       <c r="B110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110">
         <v>-0.3422</v>
@@ -4246,7 +6483,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G110">
-        <v>0.104017912336008</v>
+        <v>0.15602686850401201</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -4254,7 +6491,7 @@
         <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4269,7 +6506,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G111">
-        <v>0.104017912336008</v>
+        <v>0.15602686850401201</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -4277,7 +6514,7 @@
         <v>56</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112">
         <v>-0.3422</v>
@@ -4292,7 +6529,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G112">
-        <v>0.22727197337928801</v>
+        <v>0.34090796006893198</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -4300,7 +6537,7 @@
         <v>56</v>
       </c>
       <c r="B113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -4315,7 +6552,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G113">
-        <v>0.22727197337928801</v>
+        <v>0.34090796006893198</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -4323,7 +6560,7 @@
         <v>57</v>
       </c>
       <c r="B114" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C114">
         <v>-0.3422</v>
@@ -4338,7 +6575,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G114">
-        <v>0.181994816502413</v>
+        <v>0.27299222475361951</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -4346,7 +6583,7 @@
         <v>57</v>
       </c>
       <c r="B115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4361,7 +6598,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G115">
-        <v>0.181994816502413</v>
+        <v>0.27299222475361951</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -4369,7 +6606,7 @@
         <v>58</v>
       </c>
       <c r="B116" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116">
         <v>-0.3422</v>
@@ -4384,7 +6621,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G116">
-        <v>0.15488062489587201</v>
+        <v>0.23232093734380801</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -4392,7 +6629,7 @@
         <v>58</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -4407,7 +6644,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G117">
-        <v>0.15488062489587201</v>
+        <v>0.23232093734380801</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -4415,7 +6652,7 @@
         <v>59</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118">
         <v>-0.3422</v>
@@ -4430,7 +6667,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G118">
-        <v>0.129223912745595</v>
+        <v>0.19383586911839251</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -4438,7 +6675,7 @@
         <v>59</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -4453,7 +6690,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G119">
-        <v>0.129223912745595</v>
+        <v>0.19383586911839251</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -4461,7 +6698,7 @@
         <v>60</v>
       </c>
       <c r="B120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120">
         <v>-0.3422</v>
@@ -4476,7 +6713,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G120">
-        <v>9.5731746885326097E-2</v>
+        <v>0.14359762032798914</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -4484,7 +6721,7 @@
         <v>60</v>
       </c>
       <c r="B121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -4499,7 +6736,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G121">
-        <v>9.5731746885326097E-2</v>
+        <v>0.14359762032798914</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -4507,7 +6744,7 @@
         <v>61</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122">
         <v>-0.3422</v>
@@ -4522,7 +6759,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G122">
-        <v>0.21375978258533401</v>
+        <v>0.32063967387800102</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -4530,7 +6767,7 @@
         <v>61</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4545,7 +6782,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G123">
-        <v>0.21375978258533401</v>
+        <v>0.32063967387800102</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -4553,7 +6790,7 @@
         <v>62</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C124">
         <v>-0.3422</v>
@@ -4568,7 +6805,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G124">
-        <v>0.176059099434002</v>
+        <v>0.264088649151003</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -4576,7 +6813,7 @@
         <v>62</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -4591,7 +6828,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G125">
-        <v>0.176059099434002</v>
+        <v>0.264088649151003</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -4599,13 +6836,13 @@
         <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126">
         <v>-0.3422</v>
       </c>
       <c r="D126">
-        <v>-0.22764186127654301</v>
+        <v>-0.22764186127654298</v>
       </c>
       <c r="E126">
         <v>-8.4341824449482197E-2</v>
@@ -4614,7 +6851,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G126">
-        <v>0.14985962863222699</v>
+        <v>0.22478944294834047</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -4622,13 +6859,13 @@
         <v>63</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127">
-        <v>-0.22764186127654301</v>
+        <v>-0.22764186127654298</v>
       </c>
       <c r="E127">
         <v>-8.4341824449482197E-2</v>
@@ -4637,7 +6874,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G127">
-        <v>0.14985962863222699</v>
+        <v>0.22478944294834047</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -4645,7 +6882,7 @@
         <v>64</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128">
         <v>-0.3422</v>
@@ -4660,7 +6897,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G128">
-        <v>0.123618776092686</v>
+        <v>0.18542816413902899</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -4668,7 +6905,7 @@
         <v>64</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -4683,7 +6920,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G129">
-        <v>0.123618776092686</v>
+        <v>0.18542816413902899</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -4691,7 +6928,7 @@
         <v>65</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130">
         <v>-0.3422</v>
@@ -4706,7 +6943,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G130">
-        <v>8.5602016148145693E-2</v>
+        <v>0.12840302422221855</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -4714,7 +6951,7 @@
         <v>65</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -4729,7 +6966,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G131">
-        <v>8.5602016148145693E-2</v>
+        <v>0.12840302422221855</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -4737,7 +6974,7 @@
         <v>66</v>
       </c>
       <c r="B132" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C132">
         <v>-0.3422</v>
@@ -4752,7 +6989,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G132">
-        <v>0.203765048732165</v>
+        <v>0.30564757309824753</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -4760,7 +6997,7 @@
         <v>66</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -4775,7 +7012,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G133">
-        <v>0.203765048732165</v>
+        <v>0.30564757309824753</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -4783,7 +7020,7 @@
         <v>67</v>
       </c>
       <c r="B134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134">
         <v>-0.3422</v>
@@ -4798,7 +7035,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G134">
-        <v>0.17047041837942301</v>
+        <v>0.25570562756913451</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -4806,7 +7043,7 @@
         <v>67</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -4821,7 +7058,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G135">
-        <v>0.17047041837942301</v>
+        <v>0.25570562756913451</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -4829,7 +7066,7 @@
         <v>68</v>
       </c>
       <c r="B136" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136">
         <v>-0.3422</v>
@@ -4844,7 +7081,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G136">
-        <v>0.14483721286422699</v>
+        <v>0.21725581929634047</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -4852,7 +7089,7 @@
         <v>68</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -4867,7 +7104,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G137">
-        <v>0.14483721286422699</v>
+        <v>0.21725581929634047</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -4875,7 +7112,7 @@
         <v>69</v>
       </c>
       <c r="B138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138">
         <v>-0.3422</v>
@@ -4890,7 +7127,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G138">
-        <v>0.117659892445084</v>
+        <v>0.17648983866762599</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -4898,7 +7135,7 @@
         <v>69</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -4913,7 +7150,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G139">
-        <v>0.117659892445084</v>
+        <v>0.17648983866762599</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -4921,7 +7158,7 @@
         <v>70</v>
       </c>
       <c r="B140" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C140">
         <v>-0.3422</v>
@@ -4936,7 +7173,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G140">
-        <v>7.1787740845576403E-2</v>
+        <v>0.1076816112683646</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -4944,7 +7181,7 @@
         <v>70</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -4959,7 +7196,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G141">
-        <v>7.1787740845576403E-2</v>
+        <v>0.1076816112683646</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -4967,7 +7204,7 @@
         <v>71</v>
       </c>
       <c r="B142" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C142">
         <v>-0.3422</v>
@@ -4982,7 +7219,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G142">
-        <v>0.195555254956219</v>
+        <v>0.29333288243432853</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -4990,7 +7227,7 @@
         <v>71</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5005,7 +7242,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G143">
-        <v>0.195555254956219</v>
+        <v>0.29333288243432853</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -5013,7 +7250,7 @@
         <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C144">
         <v>-0.3422</v>
@@ -5028,7 +7265,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G144">
-        <v>0.16512702923033901</v>
+        <v>0.24769054384550851</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -5036,7 +7273,7 @@
         <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -5051,7 +7288,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G145">
-        <v>0.16512702923033901</v>
+        <v>0.24769054384550851</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -5059,7 +7296,7 @@
         <v>73</v>
       </c>
       <c r="B146" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C146">
         <v>-0.3422</v>
@@ -5074,7 +7311,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G146">
-        <v>0.139762023026136</v>
+        <v>0.20964303453920399</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -5082,7 +7319,7 @@
         <v>73</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -5097,7 +7334,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G147">
-        <v>0.139762023026136</v>
+        <v>0.20964303453920399</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -5105,7 +7342,7 @@
         <v>74</v>
       </c>
       <c r="B148" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C148">
         <v>-0.3422</v>
@@ -5120,7 +7357,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G148">
-        <v>0.11120093269147099</v>
+        <v>0.16680139903720648</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -5128,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -5143,7 +7380,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G149">
-        <v>0.11120093269147099</v>
+        <v>0.16680139903720648</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -5151,7 +7388,7 @@
         <v>75</v>
       </c>
       <c r="B150" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C150">
         <v>-0.3422</v>
@@ -5166,7 +7403,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G150">
-        <v>4.61274753373229E-2</v>
+        <v>6.9191213005984353E-2</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -5174,7 +7411,7 @@
         <v>75</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -5189,7 +7426,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G151">
-        <v>4.61274753373229E-2</v>
+        <v>6.9191213005984353E-2</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -5197,13 +7434,13 @@
         <v>76</v>
       </c>
       <c r="B152" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C152">
         <v>-0.3422</v>
       </c>
       <c r="D152">
-        <v>-0.116775990694114</v>
+        <v>-0.11677599069411401</v>
       </c>
       <c r="E152">
         <v>-4.8772850820752597E-2</v>
@@ -5212,7 +7449,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G152">
-        <v>0.244694353916348</v>
+        <v>0.36704153087452202</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -5220,13 +7457,13 @@
         <v>76</v>
       </c>
       <c r="B153" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>-0.116775990694114</v>
+        <v>-0.11677599069411401</v>
       </c>
       <c r="E153">
         <v>-4.8772850820752597E-2</v>
@@ -5235,7 +7472,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G153">
-        <v>0.244694353916348</v>
+        <v>0.36704153087452202</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -5243,7 +7480,7 @@
         <v>77</v>
       </c>
       <c r="B154" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C154">
         <v>-0.3422</v>
@@ -5258,7 +7495,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G154">
-        <v>0.18708740260917101</v>
+        <v>0.28063110391375651</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -5266,7 +7503,7 @@
         <v>77</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -5281,7 +7518,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G155">
-        <v>0.18708740260917101</v>
+        <v>0.28063110391375651</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -5289,7 +7526,7 @@
         <v>78</v>
       </c>
       <c r="B156" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C156">
         <v>-0.3422</v>
@@ -5304,7 +7541,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G156">
-        <v>0.15893075099352599</v>
+        <v>0.23839612649028899</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -5312,7 +7549,7 @@
         <v>78</v>
       </c>
       <c r="B157" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -5327,7 +7564,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G157">
-        <v>0.15893075099352599</v>
+        <v>0.23839612649028899</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -5335,7 +7572,7 @@
         <v>79</v>
       </c>
       <c r="B158" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C158">
         <v>-0.3422</v>
@@ -5350,7 +7587,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G158">
-        <v>0.133523822720131</v>
+        <v>0.20028573408019651</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -5358,7 +7595,7 @@
         <v>79</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -5373,7 +7610,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G159">
-        <v>0.133523822720131</v>
+        <v>0.20028573408019651</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -5381,13 +7618,13 @@
         <v>80</v>
       </c>
       <c r="B160" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C160">
         <v>-0.3422</v>
       </c>
       <c r="D160">
-        <v>-5.7885096561410103E-2</v>
+        <v>-5.788509656141011E-2</v>
       </c>
       <c r="E160">
         <v>-1.27006047119405E-2</v>
@@ -5396,7 +7633,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G160">
-        <v>0.102465326104138</v>
+        <v>0.153697989156207</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -5404,13 +7641,13 @@
         <v>80</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C161">
         <v>0</v>
       </c>
       <c r="D161">
-        <v>-5.7885096561410103E-2</v>
+        <v>-5.788509656141011E-2</v>
       </c>
       <c r="E161">
         <v>-1.27006047119405E-2</v>
@@ -5419,7 +7656,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G161">
-        <v>0.102465326104138</v>
+        <v>0.153697989156207</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -5427,7 +7664,7 @@
         <v>81</v>
       </c>
       <c r="B162" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C162">
         <v>-0.3422</v>
@@ -5442,7 +7679,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G162">
-        <v>0.22411885194253001</v>
+        <v>0.33617827791379501</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -5450,7 +7687,7 @@
         <v>81</v>
       </c>
       <c r="B163" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -5465,7 +7702,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G163">
-        <v>0.22411885194253001</v>
+        <v>0.33617827791379501</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -5473,7 +7710,7 @@
         <v>82</v>
       </c>
       <c r="B164" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C164">
         <v>-0.3422</v>
@@ -5488,7 +7725,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G164">
-        <v>0.180773831372468</v>
+        <v>0.27116074705870197</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -5496,7 +7733,7 @@
         <v>82</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -5511,7 +7748,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G165">
-        <v>0.180773831372468</v>
+        <v>0.27116074705870197</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -5519,7 +7756,7 @@
         <v>83</v>
       </c>
       <c r="B166" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166">
         <v>-0.3422</v>
@@ -5534,7 +7771,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G166">
-        <v>0.15387410692283299</v>
+        <v>0.23081116038424948</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
@@ -5542,7 +7779,7 @@
         <v>83</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -5557,7 +7794,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G167">
-        <v>0.15387410692283299</v>
+        <v>0.23081116038424948</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -5565,7 +7802,7 @@
         <v>84</v>
       </c>
       <c r="B168" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C168">
         <v>-0.3422</v>
@@ -5580,7 +7817,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G168">
-        <v>0.128125773991704</v>
+        <v>0.19218866098755599</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
@@ -5588,7 +7825,7 @@
         <v>84</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -5603,7 +7840,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G169">
-        <v>0.128125773991704</v>
+        <v>0.19218866098755599</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -5611,7 +7848,7 @@
         <v>85</v>
       </c>
       <c r="B170" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C170">
         <v>-0.3422</v>
@@ -5626,7 +7863,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G170">
-        <v>9.3887951832412497E-2</v>
+        <v>0.14083192774861875</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -5634,7 +7871,7 @@
         <v>85</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -5649,7 +7886,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G171">
-        <v>9.3887951832412497E-2</v>
+        <v>0.14083192774861875</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
@@ -5657,7 +7894,7 @@
         <v>86</v>
       </c>
       <c r="B172" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C172">
         <v>-0.3422</v>
@@ -5672,7 +7909,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G172">
-        <v>0.21156107931759199</v>
+        <v>0.31734161897638802</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
@@ -5680,7 +7917,7 @@
         <v>86</v>
       </c>
       <c r="B173" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -5695,7 +7932,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G173">
-        <v>0.21156107931759199</v>
+        <v>0.31734161897638802</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
@@ -5703,7 +7940,7 @@
         <v>87</v>
       </c>
       <c r="B174" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C174">
         <v>-0.3422</v>
@@ -5718,7 +7955,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G174">
-        <v>0.17491731353245399</v>
+        <v>0.26237597029868098</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
@@ -5726,7 +7963,7 @@
         <v>87</v>
       </c>
       <c r="B175" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -5741,7 +7978,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G175">
-        <v>0.17491731353245399</v>
+        <v>0.26237597029868098</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -5749,13 +7986,13 @@
         <v>88</v>
       </c>
       <c r="B176" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176">
         <v>-0.3422</v>
       </c>
-      <c r="D176" s="2" t="s">
-        <v>52</v>
+      <c r="D176" s="2">
+        <v>1.6649426669571601E-2</v>
       </c>
       <c r="E176">
         <v>-4.6276540065288502E-2</v>
@@ -5764,7 +8001,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G176">
-        <v>0.14885687793126201</v>
+        <v>0.22328531689689302</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
@@ -5772,13 +8009,13 @@
         <v>88</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
-      <c r="D177" s="2" t="s">
-        <v>52</v>
+      <c r="D177" s="2">
+        <v>1.6649426669571601E-2</v>
       </c>
       <c r="E177">
         <v>-4.6276540065288502E-2</v>
@@ -5787,7 +8024,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G177">
-        <v>0.14885687793126201</v>
+        <v>0.22328531689689302</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
@@ -5795,7 +8032,7 @@
         <v>89</v>
       </c>
       <c r="B178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C178">
         <v>-0.3422</v>
@@ -5810,7 +8047,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G178">
-        <v>0.122459213503769</v>
+        <v>0.1836888202556535</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -5818,7 +8055,7 @@
         <v>89</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -5833,7 +8070,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G179">
-        <v>0.122459213503769</v>
+        <v>0.1836888202556535</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -5841,7 +8078,7 @@
         <v>90</v>
       </c>
       <c r="B180" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C180">
         <v>-0.3422</v>
@@ -5856,7 +8093,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G180">
-        <v>8.3232221651971597E-2</v>
+        <v>0.1248483324779574</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -5864,7 +8101,7 @@
         <v>90</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -5879,7 +8116,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G181">
-        <v>8.3232221651971597E-2</v>
+        <v>0.1248483324779574</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
@@ -5887,7 +8124,7 @@
         <v>91</v>
       </c>
       <c r="B182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C182">
         <v>-0.3422</v>
@@ -5902,7 +8139,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G182">
-        <v>0.20201075259610499</v>
+        <v>0.30301612889415747</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
@@ -5910,7 +8147,7 @@
         <v>91</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -5925,7 +8162,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G183">
-        <v>0.20201075259610499</v>
+        <v>0.30301612889415747</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -5933,7 +8170,7 @@
         <v>92</v>
       </c>
       <c r="B184" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C184">
         <v>-0.3422</v>
@@ -5948,7 +8185,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G184">
-        <v>0.16938486865514099</v>
+        <v>0.25407730298271147</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -5956,7 +8193,7 @@
         <v>92</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -5971,7 +8208,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G185">
-        <v>0.16938486865514099</v>
+        <v>0.25407730298271147</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -5979,7 +8216,7 @@
         <v>93</v>
       </c>
       <c r="B186" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C186">
         <v>-0.3422</v>
@@ -5994,7 +8231,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G186">
-        <v>0.14382808310863099</v>
+        <v>0.21574212466294648</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -6002,7 +8239,7 @@
         <v>93</v>
       </c>
       <c r="B187" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -6017,7 +8254,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G187">
-        <v>0.14382808310863099</v>
+        <v>0.21574212466294648</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
@@ -6025,7 +8262,7 @@
         <v>94</v>
       </c>
       <c r="B188" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C188">
         <v>-0.3422</v>
@@ -6040,7 +8277,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G188">
-        <v>0.116413845579488</v>
+        <v>0.17462076836923202</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
@@ -6048,7 +8285,7 @@
         <v>94</v>
       </c>
       <c r="B189" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -6063,7 +8300,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G189">
-        <v>0.116413845579488</v>
+        <v>0.17462076836923202</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -6071,7 +8308,7 @@
         <v>95</v>
       </c>
       <c r="B190" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C190">
         <v>-0.3422</v>
@@ -6086,7 +8323,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G190">
-        <v>6.8180980324637097E-2</v>
+        <v>0.10227147048695565</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -6094,7 +8331,7 @@
         <v>95</v>
       </c>
       <c r="B191" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -6109,7 +8346,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G191">
-        <v>6.8180980324637097E-2</v>
+        <v>0.10227147048695565</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -6117,7 +8354,7 @@
         <v>96</v>
       </c>
       <c r="B192" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C192">
         <v>-0.3422</v>
@@ -6132,7 +8369,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G192">
-        <v>0.194057189353598</v>
+        <v>0.29108578403039698</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -6140,7 +8377,7 @@
         <v>96</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -6155,7 +8392,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G193">
-        <v>0.194057189353598</v>
+        <v>0.29108578403039698</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -6163,7 +8400,7 @@
         <v>97</v>
       </c>
       <c r="B194" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C194">
         <v>-0.3422</v>
@@ -6178,7 +8415,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G194">
-        <v>0.16408066766540599</v>
+        <v>0.246121001498109</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -6186,7 +8423,7 @@
         <v>97</v>
       </c>
       <c r="B195" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -6201,7 +8438,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G195">
-        <v>0.16408066766540599</v>
+        <v>0.246121001498109</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -6209,7 +8446,7 @@
         <v>98</v>
       </c>
       <c r="B196" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C196">
         <v>-0.3422</v>
@@ -6224,7 +8461,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G196">
-        <v>0.13873590631831301</v>
+        <v>0.20810385947746951</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -6232,7 +8469,7 @@
         <v>98</v>
       </c>
       <c r="B197" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -6247,7 +8484,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G197">
-        <v>0.13873590631831301</v>
+        <v>0.20810385947746951</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -6255,13 +8492,13 @@
         <v>99</v>
       </c>
       <c r="B198" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C198">
         <v>-0.3422</v>
       </c>
       <c r="D198">
-        <v>-0.24654607164045</v>
+        <v>-0.24654607164044998</v>
       </c>
       <c r="E198">
         <v>-7.6526749577736294E-2</v>
@@ -6270,7 +8507,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G198">
-        <v>0.109831421305519</v>
+        <v>0.1647471319582785</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -6278,13 +8515,13 @@
         <v>99</v>
       </c>
       <c r="B199" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C199">
         <v>0</v>
       </c>
       <c r="D199">
-        <v>-0.24654607164045</v>
+        <v>-0.24654607164044998</v>
       </c>
       <c r="E199">
         <v>-7.6526749577736294E-2</v>
@@ -6293,7 +8530,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G199">
-        <v>0.109831421305519</v>
+        <v>0.1647471319582785</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -6301,7 +8538,7 @@
         <v>100</v>
       </c>
       <c r="B200" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C200">
         <v>-0.3422</v>
@@ -6316,7 +8553,7 @@
         <v>0.80410000000000004</v>
       </c>
       <c r="G200">
-        <v>3.5273435603358598E-2</v>
+        <v>5.2910153405037894E-2</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -6324,7 +8561,7 @@
         <v>100</v>
       </c>
       <c r="B201" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -6354,15 +8591,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>1000</v>
@@ -6370,7 +8607,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>0.8</v>
@@ -6378,7 +8615,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4">
         <v>0.99</v>
@@ -6386,7 +8623,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -6394,7 +8631,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6">
         <v>100</v>
